--- a/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_10_9_full.xlsx
+++ b/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_10_9_full.xlsx
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -414,891 +414,1349 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>39400</v>
+        <v>38496</v>
       </c>
       <c r="B2">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="D2">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>39583</v>
+        <v>38587</v>
       </c>
       <c r="B3">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D3">
-        <v>2009</v>
-      </c>
-      <c r="E3">
-        <v>0.1825419310453436</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>39765</v>
+        <v>38678</v>
       </c>
       <c r="B4">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D4">
-        <v>2009</v>
-      </c>
-      <c r="E4">
-        <v>-0.180093374131185</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>39948</v>
+        <v>38770</v>
       </c>
       <c r="B5">
-        <v>2009</v>
-      </c>
-      <c r="C5">
-        <v>-0.009261555895478946</v>
+        <v>2006</v>
       </c>
       <c r="D5">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E5">
-        <v>0.1145211022186787</v>
+        <v>-0.8126530415420441</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>40130</v>
+        <v>38860</v>
       </c>
       <c r="B6">
-        <v>2009</v>
-      </c>
-      <c r="C6">
-        <v>0.348613976222456</v>
+        <v>2006</v>
       </c>
       <c r="D6">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E6">
-        <v>0.1555182634501051</v>
+        <v>-0.4634751819907912</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>40310</v>
+        <v>38953</v>
       </c>
       <c r="B7">
-        <v>2010</v>
-      </c>
-      <c r="C7">
-        <v>-1.404263945418582</v>
+        <v>2006</v>
       </c>
       <c r="D7">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E7">
-        <v>-0.807808220045203</v>
+        <v>0.2929493800087224</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>40494</v>
+        <v>39044</v>
       </c>
       <c r="B8">
-        <v>2010</v>
-      </c>
-      <c r="C8">
-        <v>-0.1384957661262676</v>
+        <v>2006</v>
       </c>
       <c r="D8">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E8">
-        <v>0.6938817570587785</v>
+        <v>0.8717725990275982</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>40676</v>
+        <v>39135</v>
       </c>
       <c r="B9">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C9">
-        <v>1.692932643509826</v>
+        <v>0.8919943352237336</v>
       </c>
       <c r="D9">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="E9">
-        <v>0.6262577107155831</v>
+        <v>0.9983689802211426</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>40862</v>
+        <v>39226</v>
       </c>
       <c r="B10">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C10">
-        <v>1.566479473280191</v>
+        <v>2.382020274230801</v>
       </c>
       <c r="D10">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="E10">
-        <v>0.9614071719361794</v>
+        <v>2.023754696885049</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>41044</v>
+        <v>39317</v>
       </c>
       <c r="B11">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C11">
-        <v>1.020829760720687</v>
+        <v>1.726624542314803</v>
       </c>
       <c r="D11">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="E11">
-        <v>1.148272834981245</v>
+        <v>1.640700321972788</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>41228</v>
+        <v>39408</v>
       </c>
       <c r="B12">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C12">
-        <v>0.7307568962937161</v>
+        <v>1.754772933362747</v>
       </c>
       <c r="D12">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="E12">
-        <v>1.09290550768979</v>
+        <v>1.326744712851635</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>41409</v>
+        <v>39504</v>
       </c>
       <c r="B13">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="C13">
-        <v>0.6772121200332215</v>
+        <v>0.64814444634127</v>
       </c>
       <c r="D13">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="E13">
-        <v>1.258913537332873</v>
+        <v>0.9191594057505803</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>41592</v>
+        <v>39595</v>
       </c>
       <c r="B14">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="C14">
-        <v>0.8188188121642126</v>
+        <v>1.392160100878126</v>
       </c>
       <c r="D14">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="E14">
-        <v>0.960760217268164</v>
+        <v>1.709158214173456</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>41774</v>
+        <v>39686</v>
       </c>
       <c r="B15">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C15">
-        <v>1.019715257608933</v>
+        <v>1.859713668465268</v>
       </c>
       <c r="D15">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="E15">
-        <v>0.9536145745415947</v>
+        <v>1.847054070003518</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>41957</v>
+        <v>39777</v>
       </c>
       <c r="B16">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C16">
-        <v>0.9180054319587239</v>
+        <v>2.213924989827909</v>
       </c>
       <c r="D16">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="E16">
-        <v>1.375398114243231</v>
+        <v>2.649274792682732</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>42137</v>
+        <v>39869</v>
       </c>
       <c r="B17">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C17">
-        <v>2.173959184500363</v>
+        <v>1.606463631290644</v>
       </c>
       <c r="D17">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="E17">
-        <v>1.566646323486065</v>
+        <v>1.99679149645513</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>42321</v>
+        <v>39959</v>
       </c>
       <c r="B18">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C18">
-        <v>1.9846842782967</v>
+        <v>1.012930725088279</v>
       </c>
       <c r="D18">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="E18">
-        <v>1.47327408793585</v>
+        <v>1.682215388696462</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>42503</v>
+        <v>40050</v>
       </c>
       <c r="B19">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="C19">
-        <v>1.707434489470039</v>
+        <v>2.424366838323166</v>
       </c>
       <c r="D19">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="E19">
-        <v>1.30258347990615</v>
+        <v>2.231251343269136</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>42689</v>
+        <v>40141</v>
       </c>
       <c r="B20">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="C20">
-        <v>1.755995812646982</v>
+        <v>2.534145137403332</v>
       </c>
       <c r="D20">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="E20">
-        <v>1.681032827388385</v>
+        <v>1.816269306544527</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>42867</v>
+        <v>40233</v>
       </c>
       <c r="B21">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C21">
-        <v>1.456988786619817</v>
+        <v>1.784275742501595</v>
       </c>
       <c r="D21">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="E21">
-        <v>1.84279714442821</v>
+        <v>2.256733459230453</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>43053</v>
+        <v>40319</v>
       </c>
       <c r="B22">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C22">
-        <v>1.946965557828384</v>
+        <v>2.440553594461403</v>
       </c>
       <c r="D22">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="E22">
-        <v>1.755491062323111</v>
+        <v>2.945546539872113</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>43145</v>
+        <v>40414</v>
       </c>
       <c r="B23">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C23">
-        <v>1.131202984360957</v>
+        <v>2.84124673424162</v>
       </c>
       <c r="D23">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="E23">
-        <v>1.657737120813474</v>
+        <v>3.061895993707919</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>43235</v>
+        <v>40505</v>
       </c>
       <c r="B24">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C24">
-        <v>1.241332692055597</v>
+        <v>2.088987206093629</v>
       </c>
       <c r="D24">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="E24">
-        <v>1.580042106786372</v>
+        <v>2.33227108297196</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>43326</v>
+        <v>40598</v>
       </c>
       <c r="B25">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C25">
-        <v>1.260396653238427</v>
+        <v>2.542133965768767</v>
       </c>
       <c r="D25">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="E25">
-        <v>1.567743002885069</v>
+        <v>2.461476372421889</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>43418</v>
+        <v>40687</v>
       </c>
       <c r="B26">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C26">
-        <v>1.064321453542272</v>
+        <v>1.902195691952047</v>
       </c>
       <c r="D26">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="E26">
-        <v>0.7767182380207682</v>
+        <v>2.594681811711497</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>43510</v>
+        <v>40871</v>
       </c>
       <c r="B27">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C27">
-        <v>0.5757500748109434</v>
+        <v>1.212532518945841</v>
       </c>
       <c r="D27">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="E27">
-        <v>1.030688008679626</v>
+        <v>1.839800364338995</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>43600</v>
+        <v>40963</v>
       </c>
       <c r="B28">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C28">
-        <v>1.592885137608979</v>
+        <v>1.505187323900126</v>
       </c>
       <c r="D28">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E28">
-        <v>1.604795846351492</v>
+        <v>1.526994101535628</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>43691</v>
+        <v>41053</v>
       </c>
       <c r="B29">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C29">
-        <v>1.308235387832934</v>
+        <v>1.553499676054582</v>
       </c>
       <c r="D29">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E29">
-        <v>1.242807488305697</v>
+        <v>1.311163626693634</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>43783</v>
+        <v>41144</v>
       </c>
       <c r="B30">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C30">
-        <v>1.361817904277718</v>
+        <v>1.269672160779267</v>
       </c>
       <c r="D30">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="E30">
-        <v>1.316199564471554</v>
+        <v>1.168709029049486</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>43875</v>
+        <v>41236</v>
       </c>
       <c r="B31">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C31">
-        <v>0.9437384066259158</v>
+        <v>1.196784623675229</v>
       </c>
       <c r="D31">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="E31">
-        <v>0.9049590709689692</v>
+        <v>0.6705936226832465</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>43966</v>
+        <v>41327</v>
       </c>
       <c r="B32">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C32">
-        <v>-2.015335584265165</v>
+        <v>1.50443807718057</v>
       </c>
       <c r="D32">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="E32">
-        <v>-1.215549235925817</v>
+        <v>1.569173667903545</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>44068</v>
+        <v>41418</v>
       </c>
       <c r="B33">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C33">
-        <v>-7.03958082960261</v>
+        <v>0.6194736285609848</v>
       </c>
       <c r="D33">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="E33">
-        <v>-9.851708704716611</v>
+        <v>0.7766551282351042</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>44159</v>
+        <v>41509</v>
       </c>
       <c r="B34">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C34">
-        <v>-4.352425014431327</v>
+        <v>0.7642250031508979</v>
       </c>
       <c r="D34">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="E34">
-        <v>0.9348518890383906</v>
+        <v>1.134801671545693</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>44251</v>
+        <v>41600</v>
       </c>
       <c r="B35">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C35">
-        <v>-2.824222064391535</v>
+        <v>0.4723812919182446</v>
       </c>
       <c r="D35">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="E35">
-        <v>-1.61400258701867</v>
+        <v>0.8532009935552809</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>44341</v>
+        <v>41695</v>
       </c>
       <c r="B36">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C36">
-        <v>-5.665308402785508</v>
+        <v>1.043507538863131</v>
       </c>
       <c r="D36">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E36">
-        <v>-4.458023117238186</v>
+        <v>0.8762328209637626</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>44432</v>
+        <v>41782</v>
       </c>
       <c r="B37">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C37">
-        <v>-3.576917127357704</v>
+        <v>0.4902065436673819</v>
       </c>
       <c r="D37">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E37">
-        <v>-1.507094401446352</v>
+        <v>0.7930646576103761</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>44525</v>
+        <v>41968</v>
       </c>
       <c r="B38">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C38">
-        <v>-1.761645650979182</v>
+        <v>0.8777276606119377</v>
       </c>
       <c r="D38">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="E38">
-        <v>5.161235657134755</v>
+        <v>1.473980461008906</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>44617</v>
+        <v>42059</v>
       </c>
       <c r="B39">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C39">
-        <v>2.828271820504513</v>
+        <v>1.350564852252711</v>
       </c>
       <c r="D39">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E39">
-        <v>-0.6956600178888661</v>
+        <v>0.9514122863516272</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>44706</v>
+        <v>42146</v>
       </c>
       <c r="B40">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C40">
-        <v>3.55216262984841</v>
+        <v>1.905689950888578</v>
       </c>
       <c r="D40">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E40">
-        <v>-0.5534294478199198</v>
+        <v>1.388683613675679</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>44798</v>
+        <v>42241</v>
       </c>
       <c r="B41">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C41">
-        <v>4.837108932100898</v>
+        <v>2.010391448563498</v>
       </c>
       <c r="D41">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E41">
-        <v>0.7337317298176549</v>
+        <v>1.423912797659366</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>44890</v>
+        <v>42332</v>
       </c>
       <c r="B42">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C42">
-        <v>5.20787683103745</v>
+        <v>2.290662253244125</v>
       </c>
       <c r="D42">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E42">
-        <v>2.430255857698516</v>
+        <v>2.674718982800628</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>44981</v>
+        <v>42423</v>
       </c>
       <c r="B43">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C43">
-        <v>1.970682684899994</v>
+        <v>2.746798106987303</v>
       </c>
       <c r="D43">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E43">
-        <v>5.462250257438317</v>
+        <v>2.298230956632752</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>45071</v>
+        <v>42514</v>
       </c>
       <c r="B44">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C44">
-        <v>-1.17492083522599</v>
+        <v>2.68827432811356</v>
       </c>
       <c r="D44">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E44">
-        <v>0.1140263184959744</v>
+        <v>2.207994873007224</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>45163</v>
+        <v>42606</v>
       </c>
       <c r="B45">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C45">
-        <v>-0.440616923475845</v>
+        <v>3.873983783106349</v>
       </c>
       <c r="D45">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E45">
-        <v>1.366292825135784</v>
+        <v>2.863195225581894</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>45254</v>
+        <v>42698</v>
       </c>
       <c r="B46">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C46">
-        <v>-0.9008525709169657</v>
+        <v>4.109910756223556</v>
       </c>
       <c r="D46">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E46">
-        <v>1.982587461121321</v>
+        <v>3.710877347273689</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>45345</v>
+        <v>42789</v>
       </c>
       <c r="B47">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C47">
-        <v>1.058598619486273</v>
+        <v>3.003353347662618</v>
       </c>
       <c r="D47">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E47">
-        <v>2.37789296420865</v>
+        <v>3.359512945370846</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>45436</v>
+        <v>42878</v>
       </c>
       <c r="B48">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C48">
-        <v>0.02017133142706573</v>
+        <v>1.943557593331668</v>
       </c>
       <c r="D48">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E48">
-        <v>-0.3342090768663986</v>
+        <v>2.830309762977312</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>45534</v>
+        <v>42972</v>
       </c>
       <c r="B49">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C49">
-        <v>0.5138342970629317</v>
+        <v>2.035160886298115</v>
       </c>
       <c r="D49">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E49">
-        <v>0.3554489813896833</v>
+        <v>2.634458054765276</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>45618</v>
+        <v>43062</v>
       </c>
       <c r="B50">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C50">
-        <v>0.2738544794132602</v>
+        <v>1.660180415270074</v>
       </c>
       <c r="D50">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="E50">
-        <v>-0.108077553478092</v>
+        <v>1.585737404913523</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>45713</v>
+        <v>43154</v>
       </c>
       <c r="B51">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C51">
-        <v>0.2382702494847733</v>
+        <v>2.094878531848998</v>
       </c>
       <c r="D51">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="E51">
-        <v>-0.01234339085524061</v>
+        <v>2.634625305991367</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>45800</v>
+        <v>43244</v>
       </c>
       <c r="B52">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C52">
-        <v>0.7917104405398501</v>
+        <v>1.100325026011384</v>
       </c>
       <c r="D52">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="E52">
-        <v>-0.1189552196680155</v>
+        <v>1.734997059187049</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>45891</v>
+        <v>43336</v>
       </c>
       <c r="B53">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C53">
-        <v>0.9785056085252597</v>
+        <v>1.171454932818095</v>
       </c>
       <c r="D53">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="E53">
-        <v>0.5647443720418144</v>
+        <v>1.838835801307592</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
+        <v>43427</v>
+      </c>
+      <c r="B54">
+        <v>2018</v>
+      </c>
+      <c r="C54">
+        <v>1.0578868654878</v>
+      </c>
+      <c r="D54">
+        <v>2019</v>
+      </c>
+      <c r="E54">
+        <v>1.281970873329308</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="2">
+        <v>43518</v>
+      </c>
+      <c r="B55">
+        <v>2019</v>
+      </c>
+      <c r="C55">
+        <v>2.279881099907866</v>
+      </c>
+      <c r="D55">
+        <v>2020</v>
+      </c>
+      <c r="E55">
+        <v>1.539981757526854</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="2">
+        <v>43608</v>
+      </c>
+      <c r="B56">
+        <v>2019</v>
+      </c>
+      <c r="C56">
+        <v>1.425094261273419</v>
+      </c>
+      <c r="D56">
+        <v>2020</v>
+      </c>
+      <c r="E56">
+        <v>1.138644081307949</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="2">
+        <v>43704</v>
+      </c>
+      <c r="B57">
+        <v>2019</v>
+      </c>
+      <c r="C57">
+        <v>1.738418991394841</v>
+      </c>
+      <c r="D57">
+        <v>2020</v>
+      </c>
+      <c r="E57">
+        <v>1.959439057781975</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="2">
+        <v>43791</v>
+      </c>
+      <c r="B58">
+        <v>2019</v>
+      </c>
+      <c r="C58">
+        <v>1.727536231884064</v>
+      </c>
+      <c r="D58">
+        <v>2020</v>
+      </c>
+      <c r="E58">
+        <v>2.160841232243338</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="2">
+        <v>43886</v>
+      </c>
+      <c r="B59">
+        <v>2020</v>
+      </c>
+      <c r="C59">
+        <v>2.565781289503222</v>
+      </c>
+      <c r="D59">
+        <v>2021</v>
+      </c>
+      <c r="E59">
+        <v>2.088670472418364</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="2">
+        <v>43976</v>
+      </c>
+      <c r="B60">
+        <v>2020</v>
+      </c>
+      <c r="C60">
+        <v>2.190629965965152</v>
+      </c>
+      <c r="D60">
+        <v>2021</v>
+      </c>
+      <c r="E60">
+        <v>1.960151128675891</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="2">
+        <v>44068</v>
+      </c>
+      <c r="B61">
+        <v>2020</v>
+      </c>
+      <c r="C61">
+        <v>3.201705568718727</v>
+      </c>
+      <c r="D61">
+        <v>2021</v>
+      </c>
+      <c r="E61">
+        <v>2.833937773997786</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="2">
+        <v>44159</v>
+      </c>
+      <c r="B62">
+        <v>2020</v>
+      </c>
+      <c r="C62">
+        <v>3.806466406787412</v>
+      </c>
+      <c r="D62">
+        <v>2021</v>
+      </c>
+      <c r="E62">
+        <v>3.966587736969096</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="2">
+        <v>44251</v>
+      </c>
+      <c r="B63">
+        <v>2021</v>
+      </c>
+      <c r="C63">
+        <v>1.98225894627948</v>
+      </c>
+      <c r="D63">
+        <v>2022</v>
+      </c>
+      <c r="E63">
+        <v>2.441091775535353</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="2">
+        <v>44341</v>
+      </c>
+      <c r="B64">
+        <v>2021</v>
+      </c>
+      <c r="C64">
+        <v>2.525909494668999</v>
+      </c>
+      <c r="D64">
+        <v>2022</v>
+      </c>
+      <c r="E64">
+        <v>2.956312065996869</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="2">
+        <v>44432</v>
+      </c>
+      <c r="B65">
+        <v>2021</v>
+      </c>
+      <c r="C65">
+        <v>3.333584574110748</v>
+      </c>
+      <c r="D65">
+        <v>2022</v>
+      </c>
+      <c r="E65">
+        <v>3.648626164546687</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="2">
+        <v>44525</v>
+      </c>
+      <c r="B66">
+        <v>2021</v>
+      </c>
+      <c r="C66">
+        <v>3.70707249977813</v>
+      </c>
+      <c r="D66">
+        <v>2022</v>
+      </c>
+      <c r="E66">
+        <v>2.192804028995887</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="2">
+        <v>44617</v>
+      </c>
+      <c r="B67">
+        <v>2022</v>
+      </c>
+      <c r="C67">
+        <v>2.227891908030721</v>
+      </c>
+      <c r="D67">
+        <v>2023</v>
+      </c>
+      <c r="E67">
+        <v>3.225208991926087</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="2">
+        <v>44706</v>
+      </c>
+      <c r="B68">
+        <v>2022</v>
+      </c>
+      <c r="C68">
+        <v>0.4613614749821915</v>
+      </c>
+      <c r="D68">
+        <v>2023</v>
+      </c>
+      <c r="E68">
+        <v>2.263499666078128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="2">
+        <v>44798</v>
+      </c>
+      <c r="B69">
+        <v>2022</v>
+      </c>
+      <c r="C69">
+        <v>3.683455423413418</v>
+      </c>
+      <c r="D69">
+        <v>2023</v>
+      </c>
+      <c r="E69">
+        <v>5.512037245845169</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="2">
+        <v>44890</v>
+      </c>
+      <c r="B70">
+        <v>2022</v>
+      </c>
+      <c r="C70">
+        <v>1.717176010541088</v>
+      </c>
+      <c r="D70">
+        <v>2023</v>
+      </c>
+      <c r="E70">
+        <v>2.449770370352566</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="2">
+        <v>44981</v>
+      </c>
+      <c r="B71">
+        <v>2023</v>
+      </c>
+      <c r="C71">
+        <v>1.299803737120375</v>
+      </c>
+      <c r="D71">
+        <v>2024</v>
+      </c>
+      <c r="E71">
+        <v>3.118606152226966</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="2">
+        <v>45071</v>
+      </c>
+      <c r="B72">
+        <v>2023</v>
+      </c>
+      <c r="C72">
+        <v>-4.070018373848039</v>
+      </c>
+      <c r="D72">
+        <v>2024</v>
+      </c>
+      <c r="E72">
+        <v>-2.062439327064391</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="2">
+        <v>45163</v>
+      </c>
+      <c r="B73">
+        <v>2023</v>
+      </c>
+      <c r="C73">
+        <v>-2.143497272691297</v>
+      </c>
+      <c r="D73">
+        <v>2024</v>
+      </c>
+      <c r="E73">
+        <v>-0.5974461903086259</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="2">
+        <v>45254</v>
+      </c>
+      <c r="B74">
+        <v>2023</v>
+      </c>
+      <c r="C74">
+        <v>-1.789118639096632</v>
+      </c>
+      <c r="D74">
+        <v>2024</v>
+      </c>
+      <c r="E74">
+        <v>0.09250824669828628</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="2">
+        <v>45345</v>
+      </c>
+      <c r="B75">
+        <v>2024</v>
+      </c>
+      <c r="C75">
+        <v>0.7626438877809338</v>
+      </c>
+      <c r="D75">
+        <v>2025</v>
+      </c>
+      <c r="E75">
+        <v>0.06032149049024493</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="2">
+        <v>45436</v>
+      </c>
+      <c r="B76">
+        <v>2024</v>
+      </c>
+      <c r="C76">
+        <v>1.033463848836402</v>
+      </c>
+      <c r="D76">
+        <v>2025</v>
+      </c>
+      <c r="E76">
+        <v>0.05482621034866852</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="2">
+        <v>45534</v>
+      </c>
+      <c r="B77">
+        <v>2024</v>
+      </c>
+      <c r="C77">
+        <v>2.014163563475191</v>
+      </c>
+      <c r="D77">
+        <v>2025</v>
+      </c>
+      <c r="E77">
+        <v>1.017437193711457</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="2">
+        <v>45618</v>
+      </c>
+      <c r="B78">
+        <v>2024</v>
+      </c>
+      <c r="C78">
+        <v>2.251694235954238</v>
+      </c>
+      <c r="D78">
+        <v>2025</v>
+      </c>
+      <c r="E78">
+        <v>1.536287969583872</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="2">
+        <v>45713</v>
+      </c>
+      <c r="B79">
+        <v>2025</v>
+      </c>
+      <c r="C79">
+        <v>3.098768779571448</v>
+      </c>
+      <c r="D79">
+        <v>2026</v>
+      </c>
+      <c r="E79">
+        <v>1.548220243898202</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="2">
+        <v>45800</v>
+      </c>
+      <c r="B80">
+        <v>2025</v>
+      </c>
+      <c r="C80">
+        <v>2.298988942566593</v>
+      </c>
+      <c r="D80">
+        <v>2026</v>
+      </c>
+      <c r="E80">
+        <v>1.85998739609663</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="2">
+        <v>45891</v>
+      </c>
+      <c r="B81">
+        <v>2025</v>
+      </c>
+      <c r="C81">
+        <v>2.483112516832242</v>
+      </c>
+      <c r="D81">
+        <v>2026</v>
+      </c>
+      <c r="E81">
+        <v>2.041338720980157</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="2">
         <v>45986</v>
       </c>
-      <c r="B54">
+      <c r="B82">
         <v>2025</v>
       </c>
-      <c r="C54">
-        <v>0.8976398032236155</v>
-      </c>
-      <c r="D54">
+      <c r="C82">
+        <v>2.593796720377783</v>
+      </c>
+      <c r="D82">
         <v>2026</v>
       </c>
-      <c r="E54">
-        <v>0.4275768375374467</v>
+      <c r="E82">
+        <v>2.06220747756336</v>
       </c>
     </row>
   </sheetData>
